--- a/JsonConverter/ExcelFiles/Trade.xlsx
+++ b/JsonConverter/ExcelFiles/Trade.xlsx
@@ -55,28 +55,142 @@
     <t xml:space="preserve">Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold_0001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuel_0002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplies_0003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TradingGoods_0004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TradingGoods_0005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TradingGoods_0006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TradingGoods_0007</t>
+    <t xml:space="preserve">Port_Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold_0001_Stock</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Fuel_0002</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">_Stock</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Supplies_0003</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">_Stock</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TradingGoods_0004</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">_Stock</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TradingGoods_0005</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">_Stock</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TradingGoods_0006</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">_Stock</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TradingGoods_0007</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">_Stock</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Trade_0001</t>
@@ -629,25 +743,25 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -664,25 +778,25 @@
       <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
